--- a/references_nitrate.xlsx
+++ b/references_nitrate.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10609"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jacksaville/Desktop/data 240913/240904_stds+blanks_norein_NO3_conc_noM0/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jacksaville/Documents/Paper/Data/CdD NO3/CDD-1-21_NO3/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62436B54-503D-2142-943A-B7A7D3F7E100}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C8297E8-C5E4-3045-94A7-87029E4B6907}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1180" yWindow="1600" windowWidth="44060" windowHeight="19560" xr2:uid="{90F8ED79-F1DF-4C49-B0DD-9D7371D6F505}"/>
+    <workbookView xWindow="1340" yWindow="920" windowWidth="16680" windowHeight="16300" xr2:uid="{90F8ED79-F1DF-4C49-B0DD-9D7371D6F505}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>USGS34</t>
   </si>
@@ -65,55 +65,43 @@
     <t>NICO6</t>
   </si>
   <si>
-    <t>mean_d15N</t>
-  </si>
-  <si>
-    <t>mean_d17O</t>
-  </si>
-  <si>
-    <t>mean_d18O</t>
-  </si>
-  <si>
     <t>err_d15N</t>
   </si>
   <si>
-    <t>err_d17O</t>
-  </si>
-  <si>
     <t>err_d18O</t>
   </si>
   <si>
     <t>sample_name</t>
   </si>
   <si>
-    <t>err_d18O18O</t>
-  </si>
-  <si>
-    <t>mean_d18O/15N</t>
-  </si>
-  <si>
-    <t>mean_d17O/15N</t>
-  </si>
-  <si>
-    <t>mean_d15N18O/15N</t>
-  </si>
-  <si>
-    <t>mean_d17O18O/15N</t>
-  </si>
-  <si>
-    <t>err_d18O/15N</t>
-  </si>
-  <si>
-    <t>err_d17O/15N</t>
-  </si>
-  <si>
-    <t>err_d15N18O/15N</t>
-  </si>
-  <si>
-    <t>err_d17O18O/15N</t>
-  </si>
-  <si>
-    <t>mean_d18O18O/15N</t>
+    <t>d15N</t>
+  </si>
+  <si>
+    <t>D17O</t>
+  </si>
+  <si>
+    <t>d18O</t>
+  </si>
+  <si>
+    <t>D15N18O</t>
+  </si>
+  <si>
+    <t>D17O18O</t>
+  </si>
+  <si>
+    <t>D18O18O</t>
+  </si>
+  <si>
+    <t>err_D17O</t>
+  </si>
+  <si>
+    <t>err_D15N18O</t>
+  </si>
+  <si>
+    <t>err_D18O18O</t>
+  </si>
+  <si>
+    <t>err_D17O18O</t>
   </si>
 </sst>
 </file>
@@ -123,17 +111,10 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FFC00000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -159,13 +140,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -480,7 +457,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{858B4891-00C2-C246-95BF-C212447929C6}">
-  <dimension ref="A1:Q10"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.83203125" bestFit="1" customWidth="1"/>
@@ -494,351 +471,228 @@
     <col min="17" max="17" width="12.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" t="s">
         <v>15</v>
       </c>
-      <c r="B1" t="s">
+      <c r="F1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1" t="s">
         <v>9</v>
       </c>
-      <c r="C1" t="s">
+      <c r="I1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1" t="s">
         <v>10</v>
       </c>
-      <c r="D1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G1" t="s">
+      <c r="K1" t="s">
         <v>19</v>
       </c>
-      <c r="H1" t="s">
+      <c r="L1" t="s">
+        <v>21</v>
+      </c>
+      <c r="M1" t="s">
         <v>20</v>
       </c>
-      <c r="I1" t="s">
-        <v>25</v>
-      </c>
-      <c r="J1" t="s">
-        <v>12</v>
-      </c>
-      <c r="K1" t="s">
-        <v>13</v>
-      </c>
-      <c r="L1" t="s">
-        <v>14</v>
-      </c>
-      <c r="M1" t="s">
-        <v>21</v>
-      </c>
-      <c r="N1" t="s">
-        <v>22</v>
-      </c>
-      <c r="O1" t="s">
-        <v>23</v>
-      </c>
-      <c r="P1" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3">
+      <c r="B2" s="1">
         <v>-1.8</v>
       </c>
-      <c r="C2" s="3">
-        <v>-14.8</v>
-      </c>
-      <c r="D2" s="3">
+      <c r="C2">
+        <v>-0.3</v>
+      </c>
+      <c r="D2" s="1">
         <v>-27.9</v>
       </c>
-      <c r="E2" s="3">
-        <f>1000*((D2+1000)/(B2+1000)-1)</f>
-        <v>-26.147064716489755</v>
-      </c>
-      <c r="F2" s="3">
-        <f>1000*((C2+1000)/(B2+1000)-1)</f>
-        <v>-13.02344219595275</v>
-      </c>
-      <c r="G2" s="4"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="4"/>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2" s="1">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="I2">
+        <v>0.2</v>
+      </c>
       <c r="J2" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="K2" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="L2" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="M2" s="2">
-        <f>SQRT(J2^2+L2^2)</f>
-        <v>0.42426406871192851</v>
-      </c>
-      <c r="N2" s="2">
-        <f>SQRT(K2^2+L2^2)</f>
-        <v>0.42426406871192851</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
+        <v>0.6</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3" s="1">
         <v>2.7</v>
       </c>
-      <c r="C3" s="3">
-        <v>51.5</v>
-      </c>
-      <c r="D3" s="3">
+      <c r="C3">
+        <v>21.6</v>
+      </c>
+      <c r="D3" s="1">
         <v>57.5</v>
       </c>
-      <c r="E3" s="3">
-        <f t="shared" ref="E3:E10" si="0">1000*((D3+1000)/(B3+1000)-1)</f>
-        <v>54.652438416276098</v>
-      </c>
-      <c r="F3" s="3">
-        <f>1000*((C3+1000)/(B3+1000)-1)</f>
-        <v>48.668594794055942</v>
-      </c>
-      <c r="G3" s="3">
-        <f>D3</f>
-        <v>57.5</v>
-      </c>
-      <c r="H3" s="3">
-        <f>((1000+C3)*(1000+E3)/1000)-1000</f>
-        <v>108.96703899471413</v>
-      </c>
-      <c r="I3" s="3">
-        <f>((1000+D3)*(1000+E3)/1000)-1000</f>
-        <v>115.29495362521197</v>
-      </c>
-      <c r="J3" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="K3" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="L3" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="M3" s="2">
-        <f>SQRT(J3^2+L3^2)</f>
-        <v>0.42426406871192851</v>
-      </c>
-      <c r="N3" s="2">
-        <f>SQRT(K3^2+L3^2)</f>
-        <v>0.42426406871192851</v>
-      </c>
-      <c r="O3" s="2">
-        <f>SQRT(L3^2+(J3)^2)</f>
-        <v>0.42426406871192851</v>
-      </c>
-      <c r="P3" s="2">
-        <f>SQRT(J2^2+L2^2)</f>
-        <v>0.42426406871192851</v>
-      </c>
-      <c r="Q3" s="2">
-        <f>SQRT(J2^2+L2^2)</f>
-        <v>0.42426406871192851</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="H3" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="J3">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="1">
         <v>180</v>
       </c>
-      <c r="C4" s="1"/>
       <c r="D4" s="1">
         <v>25.7</v>
       </c>
-      <c r="E4" s="3">
-        <f t="shared" si="0"/>
-        <v>-130.7627118644067</v>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4" s="1">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4" s="1">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0.2</v>
       </c>
       <c r="J4" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="M4" s="2">
-        <f t="shared" ref="M4:M10" si="1">SQRT(J4^2+L4^2)</f>
-        <v>0.42426406871192851</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+        <v>0.4</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="1">
         <v>-9.6999999999999993</v>
       </c>
-      <c r="C5" s="1"/>
       <c r="D5" s="1">
         <v>22.9</v>
       </c>
-      <c r="E5" s="3">
-        <f t="shared" si="0"/>
-        <v>32.919317378572231</v>
-      </c>
-      <c r="J5" s="1">
+      <c r="H5" s="1">
         <v>0.3</v>
       </c>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="M5" s="2">
-        <f t="shared" si="1"/>
-        <v>0.42426406871192851</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>4</v>
       </c>
       <c r="B6" s="1">
         <v>33.659999999999997</v>
       </c>
-      <c r="C6" s="1"/>
       <c r="D6" s="1">
         <v>33</v>
       </c>
-      <c r="E6" s="3">
-        <f t="shared" si="0"/>
-        <v>-0.63850782655816563</v>
-      </c>
-      <c r="J6" s="1">
+      <c r="H6" s="1">
         <v>0.3</v>
       </c>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="M6" s="2">
-        <f t="shared" si="1"/>
-        <v>0.42426406871192851</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>5</v>
       </c>
       <c r="B7" s="1">
         <v>-2.79</v>
       </c>
-      <c r="C7" s="1"/>
       <c r="D7" s="1">
         <v>-6.9</v>
       </c>
-      <c r="E7" s="3">
-        <f t="shared" si="0"/>
-        <v>-4.1214989821601877</v>
-      </c>
-      <c r="J7" s="1">
+      <c r="H7" s="1">
         <v>0.3</v>
       </c>
-      <c r="K7" s="1"/>
-      <c r="L7" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="M7" s="2">
-        <f t="shared" si="1"/>
-        <v>0.42426406871192851</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="1">
         <v>-1.8</v>
       </c>
-      <c r="C8" s="1"/>
       <c r="D8" s="1">
         <v>52.4</v>
       </c>
-      <c r="E8" s="3">
-        <f t="shared" si="0"/>
-        <v>54.297735924664359</v>
-      </c>
-      <c r="J8" s="1">
+      <c r="H8" s="1">
         <v>0.3</v>
       </c>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="M8" s="2">
-        <f t="shared" si="1"/>
-        <v>0.42426406871192851</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>7</v>
       </c>
       <c r="B9" s="1">
         <v>1.1299999999999999</v>
       </c>
-      <c r="C9" s="1"/>
       <c r="D9" s="1">
         <v>3.13</v>
       </c>
-      <c r="E9" s="3">
-        <f t="shared" si="0"/>
-        <v>1.9977425509174473</v>
-      </c>
-      <c r="J9" s="1">
+      <c r="H9" s="1">
         <v>0.3</v>
       </c>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="M9" s="2">
-        <f t="shared" si="1"/>
-        <v>0.42426406871192851</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>8</v>
       </c>
       <c r="B10" s="1">
         <v>33.700000000000003</v>
       </c>
-      <c r="C10" s="1"/>
       <c r="D10" s="1">
         <v>32.869999999999997</v>
       </c>
-      <c r="E10" s="3">
-        <f t="shared" si="0"/>
-        <v>-0.80294089194177243</v>
-      </c>
-      <c r="J10" s="1">
+      <c r="H10" s="1">
         <v>0.3</v>
-      </c>
-      <c r="K10" s="1"/>
-      <c r="L10" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="M10" s="2">
-        <f t="shared" si="1"/>
-        <v>0.42426406871192851</v>
       </c>
     </row>
   </sheetData>

--- a/references_nitrate.xlsx
+++ b/references_nitrate.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10727"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jacksaville/Documents/Paper/Data/CdD NO3/CDD-1-21_NO3/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jacksaville/Documents/Lab/Orbitrap/Data treatment/CdD16-1-21-NO3/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C8297E8-C5E4-3045-94A7-87029E4B6907}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFD726B5-AE6D-3C44-80FF-62FE5751AE0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1340" yWindow="920" windowWidth="16680" windowHeight="16300" xr2:uid="{90F8ED79-F1DF-4C49-B0DD-9D7371D6F505}"/>
+    <workbookView xWindow="1340" yWindow="500" windowWidth="16680" windowHeight="16300" xr2:uid="{90F8ED79-F1DF-4C49-B0DD-9D7371D6F505}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -624,6 +624,9 @@
       <c r="H5" s="1">
         <v>0.3</v>
       </c>
+      <c r="J5">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
@@ -638,6 +641,9 @@
       <c r="H6" s="1">
         <v>0.3</v>
       </c>
+      <c r="J6" s="1">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
@@ -652,6 +658,9 @@
       <c r="H7" s="1">
         <v>0.3</v>
       </c>
+      <c r="J7">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
@@ -666,6 +675,9 @@
       <c r="H8" s="1">
         <v>0.3</v>
       </c>
+      <c r="J8" s="1">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
@@ -680,6 +692,9 @@
       <c r="H9" s="1">
         <v>0.3</v>
       </c>
+      <c r="J9">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
@@ -693,6 +708,9 @@
       </c>
       <c r="H10" s="1">
         <v>0.3</v>
+      </c>
+      <c r="J10" s="1">
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
